--- a/artfynd/A 36230-2024 artfynd.xlsx
+++ b/artfynd/A 36230-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73695309</v>
+        <v>73695301</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446081.1395234017</v>
+        <v>445805</v>
       </c>
       <c r="R2" t="n">
-        <v>6433116.143804472</v>
+        <v>6433097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,42 +785,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73695303</v>
+        <v>73695302</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445863.9246560297</v>
+        <v>445828</v>
       </c>
       <c r="R3" t="n">
-        <v>6433098.965181496</v>
+        <v>6433094</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,62 +895,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73695314</v>
+        <v>79777970</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6A, Vg</t>
+          <t>Brandstorps distrikt, Hästebäcken, Hästhagen, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446313.0257901925</v>
+        <v>446178</v>
       </c>
       <c r="R4" t="n">
-        <v>6433119.898695607</v>
+        <v>6433135</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +961,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +991,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1044,59 +1001,62 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Sandbarrsvampar</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80559185</v>
+        <v>88666444</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hökensås naturvårdsområde, Vg</t>
+          <t>Englandssjöarna, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445839.1512977408</v>
+        <v>445801</v>
       </c>
       <c r="R5" t="n">
-        <v>6433071.766447438</v>
+        <v>6433099</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,22 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,70 +1104,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kjell Mohlin</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79777970</v>
+        <v>73695315</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brandstorps distrikt, Hästebäcken, Hästhagen, Habo kommun, Vg</t>
+          <t>6A, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446177.9546688961</v>
+        <v>446306</v>
       </c>
       <c r="R6" t="n">
-        <v>6433135.486944872</v>
+        <v>6433147</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,22 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,35 +1205,30 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Niklas Johansson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+          <t>Sandbarrsvampar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88666455</v>
+        <v>73695314</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1322,26 +1251,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Englandssjöarna, Vg</t>
+          <t>6A, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445845.4373202166</v>
+        <v>446313</v>
       </c>
       <c r="R7" t="n">
-        <v>6433065.856306966</v>
+        <v>6433120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,22 +1295,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,82 +1309,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+          <t>Sandbarrsvampar</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88666364</v>
+        <v>80559185</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Englandssjöarna, Vg</t>
+          <t>Hökensås naturvårdsområde, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446236.9237969329</v>
+        <v>445839</v>
       </c>
       <c r="R8" t="n">
-        <v>6433141.575101756</v>
+        <v>6433072</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,22 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,31 +1420,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+          <t>Kjell  Mohlin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88666362</v>
+        <v>88666366</v>
       </c>
       <c r="B9" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,21 +1447,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1592,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446080.1216370182</v>
+        <v>446095</v>
       </c>
       <c r="R9" t="n">
-        <v>6433119.334668555</v>
+        <v>6433126</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1625,19 +1515,9 @@
           <t>2020-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,19 +1549,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88666366</v>
+        <v>88666455</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1720,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446094.5360076686</v>
+        <v>445845</v>
       </c>
       <c r="R10" t="n">
-        <v>6433126.023487868</v>
+        <v>6433066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1753,19 +1628,9 @@
           <t>2020-10-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,6 +1655,3034 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>73695303</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>445864</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6433099</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>73695305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>445898</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6433112</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>73695306</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>445990</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433163</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>73695307</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>446136</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433199</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>73695308</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>446040</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433062</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>73695309</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>446081</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433116</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>73695310</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>446139</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433084</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>73695311</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>446175</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433094</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73695312</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6A, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>446277</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433170</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>79896621</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brandstorps distrikt, Hästebäcken, Hästhagen, Habo kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>446289</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433178</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>88666354</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>446219</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6433212</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>88666358</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>446249</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6433129</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88666361</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>446177</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6433085</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>88666362</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>446080</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6433119</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>88666376</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>446028</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6433055</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>88666397</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>446023</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6433035</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>88666447</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>445801</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6433099</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>88666450</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>445825</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6433098</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>88666451</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>445835</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6433101</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>88666457</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>445859</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6433108</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>88666460</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>445975</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6433152</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>88666466</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>446216</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6433195</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>88666484</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>446342</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6433132</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>88666402</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>445970</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6433014</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>88666446</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>445801</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6433099</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>88666452</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>445835</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6433101</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>88666364</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Englandssjöarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>446237</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6433142</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>

--- a/artfynd/A 36230-2024 artfynd.xlsx
+++ b/artfynd/A 36230-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695302</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79777970</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695315</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695314</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1468,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80559185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666366</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666455</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695303</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1989,6 +2049,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695306</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695307</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695308</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2319,6 +2394,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695309</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695310</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695311</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2649,6 +2739,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695312</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2768,6 +2863,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79896621</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2881,6 +2981,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666354</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2994,6 +3099,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666358</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3107,6 +3217,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666361</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3220,6 +3335,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666362</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3333,6 +3453,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666376</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3446,6 +3571,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666397</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3559,6 +3689,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666447</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3672,6 +3807,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666450</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3785,6 +3925,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666451</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3898,6 +4043,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666457</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4011,6 +4161,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666460</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4124,6 +4279,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666466</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4237,6 +4397,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666484</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4350,6 +4515,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666402</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4463,6 +4633,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666446</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4574,6 +4749,11 @@
       <c r="AY36" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666452</t>
         </is>
       </c>
     </row>
@@ -4687,8 +4867,51 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>